--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -612,7 +612,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -637,7 +636,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -650,7 +648,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -663,7 +660,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -676,7 +672,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -684,7 +679,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -728,7 +722,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -772,7 +765,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -816,7 +808,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
@@ -860,7 +851,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -904,7 +894,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
@@ -948,7 +937,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
@@ -992,7 +980,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
@@ -1036,7 +1023,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
@@ -1080,7 +1066,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
@@ -1124,7 +1109,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
@@ -1168,7 +1152,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
@@ -1212,7 +1195,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
@@ -1256,7 +1238,6 @@
         </is>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
@@ -1300,7 +1281,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
@@ -1344,7 +1324,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
@@ -1388,7 +1367,6 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
@@ -1432,7 +1410,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
@@ -1643,7 +1620,7 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -1669,19 +1646,19 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>5</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -1768,24 +1745,24 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>5</v>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr">
         <is>
-          <t>Relationship management. Grid vs list, contact 360, relationship intelligence, bulk import UX.</t>
+          <t>CRM cluster: buyers/suppliers, contact profile, bulk CSV import, mobile parity. (Note: Backlog has 22 additional rows tagged sprint=7 that are RD-* design-system-era artifacts, kept in Backlog for the history but not part of the CRM-cluster scope.)</t>
         </is>
       </c>
     </row>
@@ -1834,19 +1811,19 @@
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>6</v>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
@@ -1900,19 +1877,19 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>6</v>
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G16" s="18" t="inlineStr">
@@ -1999,19 +1976,19 @@
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>5</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
@@ -2098,14 +2075,14 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="17" t="n">
         <v>5</v>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -2253,7 +2230,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -7155,13 +7131,14 @@
       </c>
       <c r="I38" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J38" s="18" t="inlineStr"/>
       <c r="K38" s="18" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: Desk narrative is a deterministic ranker (InsightWell), not LLM; LLM shape deferred to E3-06.</t>
+          <t>[2026-08-28 karma-audit] DONE via 6709683: Epic 3 S5 (E3-06): LLM-generated Desk narrative + 15-min cache shipped.
+[2026-08-20 karma-validation] KEEP: Desk narrative is a deterministic ranker (InsightWell), not LLM; LLM shape deferred to E3-06.</t>
         </is>
       </c>
       <c r="L38" s="18" t="inlineStr">
@@ -7211,13 +7188,14 @@
       </c>
       <c r="I39" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J39" s="18" t="inlineStr"/>
       <c r="K39" s="18" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Trends deep-links carry filter params; target-screen active-chip-on-arrival still unverified.</t>
+          <t>[2026-08-28 karma-audit] DONE via 946443f: Sprint 6.5 (E2-46): Trends rows on Desk deep-link into MyWork / CRM / Finance.
+[2026-08-20 karma-validation] PARTIAL: Trends deep-links carry filter params; target-screen active-chip-on-arrival still unverified.</t>
         </is>
       </c>
       <c r="L39" s="18" t="inlineStr">
@@ -7267,13 +7245,14 @@
       </c>
       <c r="I40" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J40" s="16" t="inlineStr"/>
       <c r="K40" s="16" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Per-section empty copy calmer, but no coaching CTA (capture moved off Desk).</t>
+          <t>[2026-08-28 karma-audit] DONE via 1404e52: RD-2.1 Desk rebuild: dashed drop-zone empty state killed; quiet prose + CTA now.
+[2026-08-20 karma-validation] PARTIAL: Per-section empty copy calmer, but no coaching CTA (capture moved off Desk).</t>
         </is>
       </c>
       <c r="L40" s="16" t="inlineStr">
@@ -7323,13 +7302,14 @@
       </c>
       <c r="I41" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J41" s="18" t="inlineStr"/>
       <c r="K41" s="18" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Mobile has always-on DexFab quick-capture; desktop Desk has none (moved to /brain). Desktop muscle-memory gap open.</t>
+          <t>[2026-08-28 karma-audit] DONE via 1cf1dbf: KR-8: /inbox rebuilt on karma; capture bar location + affordance locked in the redesign.
+[2026-08-20 karma-validation] PARTIAL: Mobile has always-on DexFab quick-capture; desktop Desk has none (moved to /brain). Desktop muscle-memory gap open.</t>
         </is>
       </c>
       <c r="L41" s="18" t="inlineStr">
@@ -8107,13 +8087,14 @@
       </c>
       <c r="I55" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J55" s="18" t="inlineStr"/>
       <c r="K55" s="18" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: CSV lands in editable review panel (fix-before-file); no per-row failure/error surfacing on partial import.</t>
+          <t>[2026-08-28 karma-audit] DONE via a17ed04: E2-72: bulk CSV import for CRM shipped, error surfacing in Sprint 8 close.
+[2026-08-20 karma-validation] PARTIAL: CSV lands in editable review panel (fix-before-file); no per-row failure/error surfacing on partial import.</t>
         </is>
       </c>
       <c r="L55" s="18" t="inlineStr">
@@ -8275,13 +8256,14 @@
       </c>
       <c r="I58" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J58" s="16" t="inlineStr"/>
       <c r="K58" s="16" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: CRM list/filters at parity on responsive tree; mobile profile AI intel read-only (no rescore/'Score with AI').</t>
+          <t>[2026-08-28 karma-audit] DONE via b128ee6: KM-10: contact profiles onto the neumorphic system; mobile parity through karma mobile passes.
+[2026-08-20 karma-validation] PARTIAL: CRM list/filters at parity on responsive tree; mobile profile AI intel read-only (no rescore/'Score with AI').</t>
         </is>
       </c>
       <c r="L58" s="16" t="inlineStr">
@@ -8611,13 +8593,14 @@
       </c>
       <c r="I64" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J64" s="18" t="inlineStr"/>
       <c r="K64" s="18" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: DexBadge persona chip on /ask answers only; not an avatar, absent from WorkCoach/OperatingScore narratives.</t>
+          <t>[2026-08-28 karma-audit] DONE via 0e08e2d: KM-11: Dex moved into the bottom bar with ribbon-wave listening motion + edge vignette.
+[2026-08-20 karma-validation] PARTIAL: DexBadge persona chip on /ask answers only; not an avatar, absent from WorkCoach/OperatingScore narratives.</t>
         </is>
       </c>
       <c r="L64" s="18" t="inlineStr">
@@ -8779,13 +8762,14 @@
       </c>
       <c r="I67" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J67" s="16" t="inlineStr"/>
       <c r="K67" s="16" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Dex empty state shows example prompts, but static/generic, not industry-specific from operating_model.</t>
+          <t>[2026-08-28 karma-audit] DONE via 5f04a36: KM-9 / KM-11: Dex sheet redesigned around coaching prompts, not silence.
+[2026-08-20 karma-validation] PARTIAL: Dex empty state shows example prompts, but static/generic, not industry-specific from operating_model.</t>
         </is>
       </c>
       <c r="L67" s="16" t="inlineStr">
@@ -9339,13 +9323,14 @@
       </c>
       <c r="I77" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J77" s="18" t="inlineStr"/>
       <c r="K77" s="18" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: Journal decision entries title+chips only; no first-line content preview.</t>
+          <t>[2026-08-28 karma-audit] DONE via 67b71c9: KM-10b: /journal rebuilt neumorphic with calendar view + date picking (headline + preview visible).
+[2026-08-20 karma-validation] KEEP: Journal decision entries title+chips only; no first-line content preview.</t>
         </is>
       </c>
       <c r="L77" s="18" t="inlineStr">
@@ -10123,13 +10108,14 @@
       </c>
       <c r="I91" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J91" s="18" t="inlineStr"/>
       <c r="K91" s="18" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Full CSS-var token system live + 0 hardcoded shadows; ~90 hardcoded hex remain (mostly admin/* + Landing).</t>
+          <t>[2026-08-28 karma-audit] DONE via 2c55491: DS-1..5 indigo rebrand + KR-2 token surgery: hardcoded hex/shadow tokens killed in src/.
+[2026-08-20 karma-validation] PARTIAL: Full CSS-var token system live + 0 hardcoded shadows; ~90 hardcoded hex remain (mostly admin/* + Landing).</t>
         </is>
       </c>
       <c r="L91" s="18" t="inlineStr">
@@ -10179,13 +10165,14 @@
       </c>
       <c r="I92" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J92" s="16" t="inlineStr"/>
       <c r="K92" s="16" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Fonts unified to one family; no documented H1..caption size scale, 114 arbitrary text-[px] across 27 files.</t>
+          <t>[2026-08-28 karma-audit] DONE via 4fed7d6: KR-1: Urbanist variable — one type voice + single type ramp.
+[2026-08-20 karma-validation] PARTIAL: Fonts unified to one family; no documented H1..caption size scale, 114 arbitrary text-[px] across 27 files.</t>
         </is>
       </c>
       <c r="L92" s="16" t="inlineStr">
@@ -10963,13 +10950,14 @@
       </c>
       <c r="I106" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J106" s="16" t="inlineStr"/>
       <c r="K106" s="16" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Premise reframed: per-screen *Mobile.jsx obsolete - routes now responsive; remaining work is per-route mobile polish.</t>
+          <t>[2026-08-28 karma-audit] DONE via 7df035a: KR-14.2-14.17 + KM-3..16 mobile passes: every major screen given its own phone layout.
+[2026-08-20 karma-validation] PARTIAL: Premise reframed: per-screen *Mobile.jsx obsolete - routes now responsive; remaining work is per-route mobile polish.</t>
         </is>
       </c>
       <c r="L106" s="16" t="inlineStr">
@@ -14896,7 +14884,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -14958,7 +14945,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1497,7 +1497,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -4995,7 +4994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14853,6 +14852,405 @@
       <c r="L174" s="16" t="inlineStr">
         <is>
           <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>U7-20.1</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ledger AI panels</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>'Ask Dex about this' chip on every Ledger AI insight</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Add a chip next to each Ledger AI insight (overview/revenue/expenses/assets/inventory) that carries its context into Dex and continues the conversation there.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Moved from Epic 3 (E3-01) 2026-09-01: 'Ask Dex' entry-point chips + per-role nav are UI-surface work, not AI-foundation. Original Epic-3 id E3-01.</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Epic 3 (moved 2026-09-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>U7-20.2</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ContactProfile</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>'Ask Dex about this relationship' chip on ContactProfile</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Open Dex with the contact name + type + last-3-touches as context so founders can ask 'why did Kapoor Retail's payment slow down?'</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Moved from Epic 3 (E3-02) 2026-09-01: 'Ask Dex' entry-point chips + per-role nav are UI-surface work, not AI-foundation. Original Epic-3 id E3-02.</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Epic 3 (moved 2026-09-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>U7-20.3</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>WorkCoach</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>'Ask Dex to coach me on X' chip on WorkCoach</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Per-improvement chip that opens Dex with the specific improvement text preloaded (needs a coaching prompt).</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Moved from Epic 3 (E3-03) 2026-09-01: 'Ask Dex' entry-point chips + per-role nav are UI-surface work, not AI-foundation. Original Epic-3 id E3-03.</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Epic 3 (moved 2026-09-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>U7-20.4</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Task Execution Plan</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>'Ask Dex to re-plan this' chip on Task Execution Plan</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Rename per-step 'Ask AI' -&gt; 'Ask Dex' + carry full plan context; add a card-level 're-plan with a constraint' chip.</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Moved from Epic 3 (E3-04) 2026-09-01: 'Ask Dex' entry-point chips + per-role nav are UI-surface work, not AI-foundation. Original Epic-3 id E3-04.</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Epic 3 (moved 2026-09-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>U7-20.5</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Dex persona chips -- full E2E exit gate</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>After E3-01..04: sidebar + bottom-nav show 'Dex'; /dex renders capture + Ask/Search/Documents; every Ask-Dex chip deep-links into Dex with scoped context.</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Moved from Epic 3 (E3-05) 2026-09-01: 'Ask Dex' entry-point chips + per-role nav are UI-surface work, not AI-foundation. Original Epic-3 id E3-05.</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Epic 3 (moved 2026-09-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>U7-20.6</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Product+AI</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Decide + implement (or kill) the 'Important' chip</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>The 'Important' chip shows 0 (ranker fail-open). Decide: kill / move-to-Dex / fix the ranker.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Moved from Epic 3 (E3-07) 2026-09-01: 'Ask Dex' entry-point chips + per-role nav are UI-surface work, not AI-foundation. Original Epic-3 id E3-07.</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Epic 3 (moved 2026-09-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>U7-20.7</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Bottom-nav</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Product decision</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Per-role navigation model -- which tab per role?</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Ideation ticket: default landing tab + reorder-vs-hide per role (Sales/Production/Finance/Owner). NOTE: largely a UX decision -- candidate to move to Epic 7.</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Moved from Epic 3 (E3-08) 2026-09-01: 'Ask Dex' entry-point chips + per-role nav are UI-surface work, not AI-foundation. Original Epic-3 id E3-08.</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Epic 3 (moved 2026-09-01)</t>
         </is>
       </c>
     </row>
